--- a/templates/excel/MatchAid_PointScoring_Template.xlsx
+++ b/templates/excel/MatchAid_PointScoring_Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e0bc09bc27ca3c1c/Documents/GitHub/MatchAid_v2/Templates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e0bc09bc27ca3c1c/Documents/GitHub/MatchAid_GoDaddy/templates/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_44FF76E729690D3CAB3FAC3146487F09B56E5A68" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{973C921C-1E62-4C64-B214-B707FD02CE02}"/>
+  <xr:revisionPtr revIDLastSave="90" documentId="11_44FF76E729690D3CAB3FAC3146487F09B56E5A68" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E786CA52-0F69-4E79-8517-79708A4C6953}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,12 +63,47 @@
     <definedName name="Table2_Player4_PairingPos" localSheetId="0">'Group Template'!$A$20</definedName>
     <definedName name="Table2_Player4_Quota" localSheetId="0">'Group Template'!$C$20</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="23">
   <si>
     <t>Group</t>
   </si>
@@ -95,13 +130,55 @@
   </si>
   <si>
     <t>Total Points</t>
+  </si>
+  <si>
+    <t>PLAYER</t>
+  </si>
+  <si>
+    <t>QUOTA</t>
+  </si>
+  <si>
+    <t>POINTS</t>
+  </si>
+  <si>
+    <t>Eagle</t>
+  </si>
+  <si>
+    <t>Birdie</t>
+  </si>
+  <si>
+    <t>Par</t>
+  </si>
+  <si>
+    <t>Bogie</t>
+  </si>
+  <si>
+    <t>Double</t>
+  </si>
+  <si>
+    <t>Triple</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>TOTAL QUOTA</t>
+  </si>
+  <si>
+    <t>H 1-6</t>
+  </si>
+  <si>
+    <t>H 7-12</t>
+  </si>
+  <si>
+    <t>H 13-18</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -124,8 +201,21 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -155,8 +245,20 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -264,11 +366,280 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -303,34 +674,133 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="5" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="5" fillId="6" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -506,7 +976,7 @@
   <sheetPr codeName="worksheet_Tab00">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:17" ht="18" x14ac:dyDescent="0.3">
@@ -552,9 +1022,9 @@
       </c>
     </row>
     <row r="3" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="15"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
+      <c r="A3" s="17"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
       <c r="D3" s="5" t="s">
         <v>7</v>
       </c>
@@ -569,13 +1039,13 @@
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
       <c r="O3" s="7"/>
-      <c r="P3" s="17"/>
-      <c r="Q3" s="19"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="14"/>
     </row>
     <row r="4" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
+      <c r="A4" s="18"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
       <c r="D4" s="8" t="s">
         <v>6</v>
       </c>
@@ -590,13 +1060,13 @@
       <c r="M4" s="9"/>
       <c r="N4" s="10"/>
       <c r="O4" s="9"/>
-      <c r="P4" s="18"/>
-      <c r="Q4" s="20"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="15"/>
     </row>
     <row r="5" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="15"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
       <c r="D5" s="5" t="s">
         <v>7</v>
       </c>
@@ -611,13 +1081,13 @@
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
       <c r="O5" s="7"/>
-      <c r="P5" s="18"/>
-      <c r="Q5" s="20"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="15"/>
     </row>
     <row r="6" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="16"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
       <c r="D6" s="8" t="s">
         <v>6</v>
       </c>
@@ -632,13 +1102,13 @@
       <c r="M6" s="9"/>
       <c r="N6" s="10"/>
       <c r="O6" s="9"/>
-      <c r="P6" s="18"/>
-      <c r="Q6" s="20"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="15"/>
     </row>
     <row r="7" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="15"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
       <c r="D7" s="5" t="s">
         <v>7</v>
       </c>
@@ -653,13 +1123,13 @@
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
       <c r="O7" s="7"/>
-      <c r="P7" s="18"/>
-      <c r="Q7" s="20"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="15"/>
     </row>
     <row r="8" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="16"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
+      <c r="A8" s="18"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
       <c r="D8" s="8" t="s">
         <v>6</v>
       </c>
@@ -674,13 +1144,13 @@
       <c r="M8" s="9"/>
       <c r="N8" s="10"/>
       <c r="O8" s="9"/>
-      <c r="P8" s="18"/>
-      <c r="Q8" s="20"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="15"/>
     </row>
     <row r="9" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="15"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
       <c r="D9" s="5" t="s">
         <v>7</v>
       </c>
@@ -695,13 +1165,13 @@
       <c r="M9" s="6"/>
       <c r="N9" s="6"/>
       <c r="O9" s="7"/>
-      <c r="P9" s="18"/>
-      <c r="Q9" s="20"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="15"/>
     </row>
     <row r="10" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="16"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
       <c r="D10" s="8" t="s">
         <v>6</v>
       </c>
@@ -716,16 +1186,16 @@
       <c r="M10" s="9"/>
       <c r="N10" s="10"/>
       <c r="O10" s="9"/>
-      <c r="P10" s="18"/>
-      <c r="Q10" s="21"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="16"/>
     </row>
     <row r="11" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
@@ -740,7 +1210,7 @@
       <c r="P11" s="6"/>
       <c r="Q11" s="6"/>
     </row>
-    <row r="12" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" s="4" customFormat="1" ht="7.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11"/>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -795,9 +1265,9 @@
       </c>
     </row>
     <row r="14" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="15"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
+      <c r="A14" s="17"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
       <c r="D14" s="5" t="s">
         <v>7</v>
       </c>
@@ -812,13 +1282,13 @@
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
       <c r="O14" s="7"/>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="19"/>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="14"/>
     </row>
     <row r="15" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="16"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
+      <c r="A15" s="18"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
       <c r="D15" s="8" t="s">
         <v>6</v>
       </c>
@@ -833,13 +1303,13 @@
       <c r="M15" s="9"/>
       <c r="N15" s="10"/>
       <c r="O15" s="9"/>
-      <c r="P15" s="18"/>
-      <c r="Q15" s="20"/>
+      <c r="P15" s="13"/>
+      <c r="Q15" s="15"/>
     </row>
     <row r="16" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="15"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
+      <c r="A16" s="17"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
       <c r="D16" s="5" t="s">
         <v>7</v>
       </c>
@@ -854,13 +1324,13 @@
       <c r="M16" s="6"/>
       <c r="N16" s="6"/>
       <c r="O16" s="7"/>
-      <c r="P16" s="18"/>
-      <c r="Q16" s="20"/>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="15"/>
     </row>
     <row r="17" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="16"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
+      <c r="A17" s="18"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
       <c r="D17" s="8" t="s">
         <v>6</v>
       </c>
@@ -875,13 +1345,13 @@
       <c r="M17" s="9"/>
       <c r="N17" s="10"/>
       <c r="O17" s="9"/>
-      <c r="P17" s="18"/>
-      <c r="Q17" s="20"/>
+      <c r="P17" s="13"/>
+      <c r="Q17" s="15"/>
     </row>
     <row r="18" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="15"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
+      <c r="A18" s="17"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
       <c r="D18" s="5" t="s">
         <v>7</v>
       </c>
@@ -896,13 +1366,13 @@
       <c r="M18" s="6"/>
       <c r="N18" s="6"/>
       <c r="O18" s="7"/>
-      <c r="P18" s="18"/>
-      <c r="Q18" s="20"/>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="15"/>
     </row>
     <row r="19" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="16"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
+      <c r="A19" s="18"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
       <c r="D19" s="8" t="s">
         <v>6</v>
       </c>
@@ -917,13 +1387,13 @@
       <c r="M19" s="9"/>
       <c r="N19" s="10"/>
       <c r="O19" s="9"/>
-      <c r="P19" s="18"/>
-      <c r="Q19" s="20"/>
+      <c r="P19" s="13"/>
+      <c r="Q19" s="15"/>
     </row>
     <row r="20" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="15"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
+      <c r="A20" s="17"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
       <c r="D20" s="5" t="s">
         <v>7</v>
       </c>
@@ -938,13 +1408,13 @@
       <c r="M20" s="6"/>
       <c r="N20" s="6"/>
       <c r="O20" s="7"/>
-      <c r="P20" s="18"/>
-      <c r="Q20" s="20"/>
+      <c r="P20" s="13"/>
+      <c r="Q20" s="15"/>
     </row>
     <row r="21" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="16"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
+      <c r="A21" s="18"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
       <c r="D21" s="8" t="s">
         <v>6</v>
       </c>
@@ -959,16 +1429,16 @@
       <c r="M21" s="9"/>
       <c r="N21" s="10"/>
       <c r="O21" s="9"/>
-      <c r="P21" s="18"/>
-      <c r="Q21" s="21"/>
+      <c r="P21" s="13"/>
+      <c r="Q21" s="16"/>
     </row>
     <row r="22" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
@@ -983,8 +1453,164 @@
       <c r="P22" s="6"/>
       <c r="Q22" s="6"/>
     </row>
+    <row r="23" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="24" spans="1:17" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="32"/>
+      <c r="C24" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="51" t="s">
+        <v>20</v>
+      </c>
+      <c r="G24" s="52" t="s">
+        <v>21</v>
+      </c>
+      <c r="H24" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="O24" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="P24" s="32"/>
+      <c r="Q24" s="33" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="30" cm="1">
+        <f t="array" ref="A25">_xlfn.UNIQUE(B3:B10)</f>
+        <v>0</v>
+      </c>
+      <c r="B25" s="22"/>
+      <c r="C25" s="25">
+        <f>IF(A25&lt;&gt;"",SUMIF(B3:B10,A25),"")</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="48"/>
+      <c r="G25" s="48"/>
+      <c r="H25" s="49"/>
+      <c r="I25" s="50"/>
+      <c r="O25" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="P25" s="22"/>
+      <c r="Q25" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="34"/>
+      <c r="B26" s="35"/>
+      <c r="C26" s="36"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="37"/>
+      <c r="H26" s="23"/>
+      <c r="I26" s="36"/>
+      <c r="O26" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="34"/>
+      <c r="B27" s="35"/>
+      <c r="C27" s="36"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="37"/>
+      <c r="H27" s="23"/>
+      <c r="I27" s="36"/>
+      <c r="O27" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="P27" s="22"/>
+      <c r="Q27" s="25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="38"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="40"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="42"/>
+      <c r="I28" s="43"/>
+      <c r="O28" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="P28" s="22"/>
+      <c r="Q28" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="B29" s="45"/>
+      <c r="C29" s="46">
+        <f>SUM(C25:C28)</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="47"/>
+      <c r="G29" s="47"/>
+      <c r="H29" s="47"/>
+      <c r="I29" s="47"/>
+      <c r="O29" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="P29" s="22"/>
+      <c r="Q29" s="26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="O30" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="P30" s="28"/>
+      <c r="Q30" s="29">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="43">
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="O28:P28"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="C14:C15"/>
     <mergeCell ref="P3:P10"/>
     <mergeCell ref="Q3:Q10"/>
     <mergeCell ref="A14:A15"/>
@@ -1001,26 +1627,13 @@
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="C7:C8"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="C14:C15"/>
   </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="85" orientation="landscape" r:id="rId1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.53" bottom="0.22" header="0.22" footer="0.18"/>
+  <pageSetup scale="75" orientation="landscape" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;CMatchAid
-Point Scoring Template</oddHeader>
+Point Scoring Template - 9's</oddHeader>
   </headerFooter>
 </worksheet>
 </file>
--- a/templates/excel/MatchAid_PointScoring_Template.xlsx
+++ b/templates/excel/MatchAid_PointScoring_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e0bc09bc27ca3c1c/Documents/GitHub/MatchAid_GoDaddy/templates/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="90" documentId="11_44FF76E729690D3CAB3FAC3146487F09B56E5A68" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E786CA52-0F69-4E79-8517-79708A4C6953}"/>
+  <xr:revisionPtr revIDLastSave="92" documentId="11_44FF76E729690D3CAB3FAC3146487F09B56E5A68" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0DD8B30-A881-428A-A14B-02DF8F5E5162}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,8 +16,7 @@
     <sheet name="Group Template" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Group_PairingID" localSheetId="0">'Group Template'!$B$1</definedName>
-    <definedName name="Group_PlayerKey">'Group Template'!$B$1</definedName>
+    <definedName name="Group_PlayerKey" localSheetId="0">'Group Template'!$B$1</definedName>
     <definedName name="Table1" localSheetId="0">'Group Template'!$A$2:$Q$11</definedName>
     <definedName name="Table1_Hole01" localSheetId="0">'Group Template'!$E$2</definedName>
     <definedName name="Table1_Hole02" localSheetId="0">'Group Template'!$F$2</definedName>
@@ -639,7 +638,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -674,20 +673,110 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="5" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="5" fillId="6" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -695,112 +784,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="5" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="5" fillId="6" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1022,9 +1018,9 @@
       </c>
     </row>
     <row r="3" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="17"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
+      <c r="A3" s="47"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
       <c r="D3" s="5" t="s">
         <v>7</v>
       </c>
@@ -1039,13 +1035,13 @@
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
       <c r="O3" s="7"/>
-      <c r="P3" s="12"/>
-      <c r="Q3" s="14"/>
+      <c r="P3" s="49"/>
+      <c r="Q3" s="51"/>
     </row>
     <row r="4" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="18"/>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
+      <c r="A4" s="48"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
       <c r="D4" s="8" t="s">
         <v>6</v>
       </c>
@@ -1060,13 +1056,13 @@
       <c r="M4" s="9"/>
       <c r="N4" s="10"/>
       <c r="O4" s="9"/>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="15"/>
+      <c r="P4" s="50"/>
+      <c r="Q4" s="52"/>
     </row>
     <row r="5" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="17"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
+      <c r="A5" s="47"/>
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
       <c r="D5" s="5" t="s">
         <v>7</v>
       </c>
@@ -1081,13 +1077,13 @@
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
       <c r="O5" s="7"/>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="15"/>
+      <c r="P5" s="50"/>
+      <c r="Q5" s="52"/>
     </row>
     <row r="6" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="18"/>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
+      <c r="A6" s="48"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="46"/>
       <c r="D6" s="8" t="s">
         <v>6</v>
       </c>
@@ -1102,13 +1098,13 @@
       <c r="M6" s="9"/>
       <c r="N6" s="10"/>
       <c r="O6" s="9"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="15"/>
+      <c r="P6" s="50"/>
+      <c r="Q6" s="52"/>
     </row>
     <row r="7" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="17"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
+      <c r="A7" s="47"/>
+      <c r="B7" s="45"/>
+      <c r="C7" s="45"/>
       <c r="D7" s="5" t="s">
         <v>7</v>
       </c>
@@ -1123,13 +1119,13 @@
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
       <c r="O7" s="7"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="15"/>
+      <c r="P7" s="50"/>
+      <c r="Q7" s="52"/>
     </row>
     <row r="8" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="18"/>
-      <c r="B8" s="20"/>
-      <c r="C8" s="20"/>
+      <c r="A8" s="48"/>
+      <c r="B8" s="46"/>
+      <c r="C8" s="46"/>
       <c r="D8" s="8" t="s">
         <v>6</v>
       </c>
@@ -1144,13 +1140,13 @@
       <c r="M8" s="9"/>
       <c r="N8" s="10"/>
       <c r="O8" s="9"/>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="15"/>
+      <c r="P8" s="50"/>
+      <c r="Q8" s="52"/>
     </row>
     <row r="9" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="17"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
+      <c r="A9" s="47"/>
+      <c r="B9" s="45"/>
+      <c r="C9" s="45"/>
       <c r="D9" s="5" t="s">
         <v>7</v>
       </c>
@@ -1165,13 +1161,13 @@
       <c r="M9" s="6"/>
       <c r="N9" s="6"/>
       <c r="O9" s="7"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="15"/>
+      <c r="P9" s="50"/>
+      <c r="Q9" s="52"/>
     </row>
     <row r="10" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="18"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
+      <c r="A10" s="48"/>
+      <c r="B10" s="46"/>
+      <c r="C10" s="46"/>
       <c r="D10" s="8" t="s">
         <v>6</v>
       </c>
@@ -1186,16 +1182,16 @@
       <c r="M10" s="9"/>
       <c r="N10" s="10"/>
       <c r="O10" s="9"/>
-      <c r="P10" s="13"/>
-      <c r="Q10" s="16"/>
+      <c r="P10" s="50"/>
+      <c r="Q10" s="53"/>
     </row>
     <row r="11" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
@@ -1265,9 +1261,9 @@
       </c>
     </row>
     <row r="14" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="17"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
+      <c r="A14" s="47"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
       <c r="D14" s="5" t="s">
         <v>7</v>
       </c>
@@ -1282,13 +1278,13 @@
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
       <c r="O14" s="7"/>
-      <c r="P14" s="12"/>
-      <c r="Q14" s="14"/>
+      <c r="P14" s="49"/>
+      <c r="Q14" s="51"/>
     </row>
     <row r="15" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="18"/>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
+      <c r="A15" s="48"/>
+      <c r="B15" s="46"/>
+      <c r="C15" s="46"/>
       <c r="D15" s="8" t="s">
         <v>6</v>
       </c>
@@ -1303,13 +1299,13 @@
       <c r="M15" s="9"/>
       <c r="N15" s="10"/>
       <c r="O15" s="9"/>
-      <c r="P15" s="13"/>
-      <c r="Q15" s="15"/>
+      <c r="P15" s="50"/>
+      <c r="Q15" s="52"/>
     </row>
     <row r="16" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="17"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
+      <c r="A16" s="47"/>
+      <c r="B16" s="45"/>
+      <c r="C16" s="45"/>
       <c r="D16" s="5" t="s">
         <v>7</v>
       </c>
@@ -1324,13 +1320,13 @@
       <c r="M16" s="6"/>
       <c r="N16" s="6"/>
       <c r="O16" s="7"/>
-      <c r="P16" s="13"/>
-      <c r="Q16" s="15"/>
+      <c r="P16" s="50"/>
+      <c r="Q16" s="52"/>
     </row>
     <row r="17" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="18"/>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
+      <c r="A17" s="48"/>
+      <c r="B17" s="46"/>
+      <c r="C17" s="46"/>
       <c r="D17" s="8" t="s">
         <v>6</v>
       </c>
@@ -1345,13 +1341,13 @@
       <c r="M17" s="9"/>
       <c r="N17" s="10"/>
       <c r="O17" s="9"/>
-      <c r="P17" s="13"/>
-      <c r="Q17" s="15"/>
+      <c r="P17" s="50"/>
+      <c r="Q17" s="52"/>
     </row>
     <row r="18" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="17"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
+      <c r="A18" s="47"/>
+      <c r="B18" s="45"/>
+      <c r="C18" s="45"/>
       <c r="D18" s="5" t="s">
         <v>7</v>
       </c>
@@ -1366,13 +1362,13 @@
       <c r="M18" s="6"/>
       <c r="N18" s="6"/>
       <c r="O18" s="7"/>
-      <c r="P18" s="13"/>
-      <c r="Q18" s="15"/>
+      <c r="P18" s="50"/>
+      <c r="Q18" s="52"/>
     </row>
     <row r="19" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="18"/>
-      <c r="B19" s="20"/>
-      <c r="C19" s="20"/>
+      <c r="A19" s="48"/>
+      <c r="B19" s="46"/>
+      <c r="C19" s="46"/>
       <c r="D19" s="8" t="s">
         <v>6</v>
       </c>
@@ -1387,13 +1383,13 @@
       <c r="M19" s="9"/>
       <c r="N19" s="10"/>
       <c r="O19" s="9"/>
-      <c r="P19" s="13"/>
-      <c r="Q19" s="15"/>
+      <c r="P19" s="50"/>
+      <c r="Q19" s="52"/>
     </row>
     <row r="20" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="17"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
+      <c r="A20" s="47"/>
+      <c r="B20" s="45"/>
+      <c r="C20" s="45"/>
       <c r="D20" s="5" t="s">
         <v>7</v>
       </c>
@@ -1408,13 +1404,13 @@
       <c r="M20" s="6"/>
       <c r="N20" s="6"/>
       <c r="O20" s="7"/>
-      <c r="P20" s="13"/>
-      <c r="Q20" s="15"/>
+      <c r="P20" s="50"/>
+      <c r="Q20" s="52"/>
     </row>
     <row r="21" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="18"/>
-      <c r="B21" s="20"/>
-      <c r="C21" s="20"/>
+      <c r="A21" s="48"/>
+      <c r="B21" s="46"/>
+      <c r="C21" s="46"/>
       <c r="D21" s="8" t="s">
         <v>6</v>
       </c>
@@ -1429,16 +1425,16 @@
       <c r="M21" s="9"/>
       <c r="N21" s="10"/>
       <c r="O21" s="9"/>
-      <c r="P21" s="13"/>
-      <c r="Q21" s="16"/>
+      <c r="P21" s="50"/>
+      <c r="Q21" s="53"/>
     </row>
     <row r="22" spans="1:17" s="4" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
+      <c r="B22" s="44"/>
+      <c r="C22" s="44"/>
+      <c r="D22" s="44"/>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
@@ -1455,162 +1451,135 @@
     </row>
     <row r="23" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="24" spans="1:17" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="31" t="s">
+      <c r="A24" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="B24" s="32"/>
-      <c r="C24" s="33" t="s">
+      <c r="B24" s="38"/>
+      <c r="C24" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="F24" s="51" t="s">
+      <c r="F24" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="G24" s="52" t="s">
+      <c r="G24" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="H24" s="53" t="s">
+      <c r="H24" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="54" t="s">
+      <c r="I24" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="O24" s="31" t="s">
+      <c r="O24" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="P24" s="32"/>
-      <c r="Q24" s="33" t="s">
+      <c r="P24" s="38"/>
+      <c r="Q24" s="15" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:17" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="30" cm="1">
+      <c r="A25" s="39" cm="1">
         <f t="array" ref="A25">_xlfn.UNIQUE(B3:B10)</f>
         <v>0</v>
       </c>
-      <c r="B25" s="22"/>
-      <c r="C25" s="25">
+      <c r="B25" s="32"/>
+      <c r="C25" s="13">
         <f>IF(A25&lt;&gt;"",SUMIF(B3:B10,A25),"")</f>
         <v>0</v>
       </c>
-      <c r="F25" s="48"/>
-      <c r="G25" s="48"/>
-      <c r="H25" s="49"/>
-      <c r="I25" s="50"/>
-      <c r="O25" s="24" t="s">
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="26"/>
+      <c r="O25" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="P25" s="22"/>
-      <c r="Q25" s="25">
+      <c r="P25" s="32"/>
+      <c r="Q25" s="13">
         <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:17" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="34"/>
-      <c r="B26" s="35"/>
-      <c r="C26" s="36"/>
-      <c r="F26" s="37"/>
-      <c r="G26" s="37"/>
-      <c r="H26" s="23"/>
-      <c r="I26" s="36"/>
-      <c r="O26" s="24" t="s">
+      <c r="A26" s="40"/>
+      <c r="B26" s="41"/>
+      <c r="C26" s="17"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="17"/>
+      <c r="O26" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="P26" s="22"/>
-      <c r="Q26" s="25">
+      <c r="P26" s="32"/>
+      <c r="Q26" s="13">
         <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:17" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="34"/>
-      <c r="B27" s="35"/>
-      <c r="C27" s="36"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="23"/>
-      <c r="I27" s="36"/>
-      <c r="O27" s="24" t="s">
+      <c r="A27" s="40"/>
+      <c r="B27" s="41"/>
+      <c r="C27" s="17"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="17"/>
+      <c r="O27" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="P27" s="22"/>
-      <c r="Q27" s="25">
+      <c r="P27" s="32"/>
+      <c r="Q27" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:17" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="38"/>
-      <c r="B28" s="39"/>
-      <c r="C28" s="40"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="42"/>
-      <c r="I28" s="43"/>
-      <c r="O28" s="24" t="s">
+      <c r="A28" s="42"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="18"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="21"/>
+      <c r="O28" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="P28" s="22"/>
-      <c r="Q28" s="25">
+      <c r="P28" s="32"/>
+      <c r="Q28" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:17" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="44" t="s">
+      <c r="A29" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="B29" s="45"/>
-      <c r="C29" s="46">
+      <c r="B29" s="36"/>
+      <c r="C29" s="22">
         <f>SUM(C25:C28)</f>
         <v>0</v>
       </c>
-      <c r="F29" s="47"/>
-      <c r="G29" s="47"/>
-      <c r="H29" s="47"/>
-      <c r="I29" s="47"/>
-      <c r="O29" s="24" t="s">
+      <c r="F29" s="23"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="23"/>
+      <c r="I29" s="23"/>
+      <c r="O29" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="P29" s="22"/>
-      <c r="Q29" s="26">
+      <c r="P29" s="32"/>
+      <c r="Q29" s="13">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:17" s="4" customFormat="1" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="O30" s="27" t="s">
+      <c r="O30" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="P30" s="28"/>
-      <c r="Q30" s="29">
+      <c r="P30" s="34"/>
+      <c r="Q30" s="14">
         <v>-1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="O29:P29"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="O25:P25"/>
-    <mergeCell ref="O26:P26"/>
-    <mergeCell ref="O27:P27"/>
-    <mergeCell ref="O28:P28"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="C14:C15"/>
     <mergeCell ref="P3:P10"/>
     <mergeCell ref="Q3:Q10"/>
     <mergeCell ref="A14:A15"/>
@@ -1627,6 +1596,33 @@
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="C7:C8"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="O28:P28"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A24:B24"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.53" bottom="0.22" header="0.22" footer="0.18"/>
